--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0237.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0237.xlsx
@@ -15471,7 +15471,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Tất Cả Ra Trận! Vươn Tới Đỉnh Danh Vọng</t>
+          <t>Tất Cả Vào Cuộc! Vươn Tới Đỉnh Danh Vọng</t>
         </is>
       </c>
     </row>
